--- a/Train_A_Skill/Level1_Skill_Vertical_StraightArmPull_HangingLSit.xlsx
+++ b/Train_A_Skill/Level1_Skill_Vertical_StraightArmPull_HangingLSit.xlsx
@@ -93,7 +93,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -117,6 +117,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFE599"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFEAF6E1"/>
       </patternFill>
     </fill>
@@ -133,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -162,16 +167,19 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -539,348 +547,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="8.710000000000001" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="31.5" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>TRAIN A SKILL — LEVEL 1  ·  HANGING L SIT  ·  PHASE 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Self-paced — stay on each exercise until the standard is earned. Train inside the PRESCRIPTION range; the top of the range is the STANDARD. Phase 1 = the 0 exercises + the grade 1 exercises. ◇ PICK 1 = choose one. Every cell is a per-set prescription.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="21.75" customHeight="1">
-      <c r="A4" s="3" t="n"/>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>EXERCISE</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>STANDARD</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>PRESCRIPTION</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18.75" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>PHASE 1 · VERTICAL STRAIGHT ARM PULL · 2 sets</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>◇  PICK 1  —  interchangeable, choose one</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>○  1</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>Passive Hang</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>1 minute hold, full decompression</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="inlineStr">
-        <is>
-          <t>30–60s</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>○  1</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Feet Assisted Scapula Pull-ups</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>15 reps</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>12–15 reps</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>○  1</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Active Hang Hold</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>45s hold, scapula depression</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>20–45s</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>○  1</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Scapula Pull-ups</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>15 reps, 1s hold at top</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>5–15 reps</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>○  1</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>Feet Assisted Arching Active Hang</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>15 reps, arms straight</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>5–15 reps</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>○  0</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>1 Arm Cable Scapular Pulldown</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>10 reps at 40% bodyweight</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>8–10 reps @ 15–20% BW</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>○  0</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Overhead banded Pullaparts</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>20 reps with a medium resistance band</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>20 reps · light–medium resistance band</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>○  0</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Banded Pull Aparts</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>15 reps medium resistance band</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>15 reps · light–medium resistance band</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>○  0</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Banded Pulldowns</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>20 reps with medium intensity band</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>20 reps · light–medium resistance band</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>○  0</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Lateral Cable Pulldowns</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>12 reps with 15% bodyweight</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>12 reps @ 5–15% BW</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>○  0</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>DB Lat Pullover</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>12 reps with 15% bodyweight</t>
-        </is>
-      </c>
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>12 reps @ 5–15% BW</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="D10:F10"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId11"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
   <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -895,14 +561,14 @@
     <row r="1" ht="31.5" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TRAIN A SKILL — LEVEL 1  ·  HANGING L SIT  ·  PHASE 2</t>
+          <t>TRAIN A SKILL — LEVEL 1  ·  HANGING L SIT  ·  PHASE 1</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Self-paced — stay on each exercise until the standard is earned. Train inside the PRESCRIPTION range; the top of the range is the STANDARD. Phase 2 = the 0 exercises + the grade 2 exercises. ◇ PICK 1 = choose one. Every cell is a per-set prescription.</t>
+          <t>Self-paced — stay on each exercise until the standard is earned. Train inside the PRESCRIPTION range; the top of the range is the STANDARD. Phase 1 = the 0 exercises + the grade 1 exercises. ◇ PICK 1 = choose one. Every cell is a per-set prescription.</t>
         </is>
       </c>
     </row>
@@ -927,7 +593,7 @@
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>PHASE 2 · VERTICAL STRAIGHT ARM PULL · 2 sets</t>
+          <t>PHASE 1 · VERTICAL STRAIGHT ARM PULL · 2 sets</t>
         </is>
       </c>
     </row>
@@ -941,44 +607,44 @@
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>○  2</t>
+          <t>○  1</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Active Tuck Hang Reps</t>
+          <t>Passive Hang</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>15 reps, knees in line with hips</t>
+          <t>1 minute hold, full decompression</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>5–15 reps</t>
+          <t>30–60s</t>
         </is>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>○  2</t>
+          <t>○  1</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Active Tuck Hang Hold</t>
+          <t>Feet Assisted Scapula Pull-ups</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>45s hold, knees in line with hips</t>
+          <t>15 reps</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>20–45s</t>
+          <t>12–15 reps</t>
         </is>
       </c>
     </row>
@@ -1000,7 +666,7 @@
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>8–10 reps @ 20–30% BW</t>
+          <t>8–10 reps @ 15–20% BW</t>
         </is>
       </c>
     </row>
@@ -1145,13 +811,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1165,14 +831,14 @@
     <row r="1" ht="31.5" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TRAIN A SKILL — LEVEL 1  ·  HANGING L SIT  ·  PHASE 3</t>
+          <t>TRAIN A SKILL — LEVEL 1  ·  HANGING L SIT  ·  PHASE 2</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Self-paced — stay on each exercise until the standard is earned. Train inside the PRESCRIPTION range; the top of the range is the STANDARD. Phase 3 = the 0 exercises + the grade 3 exercises. ◇ PICK 1 = choose one. Every cell is a per-set prescription.</t>
+          <t>Self-paced — stay on each exercise until the standard is earned. Train inside the PRESCRIPTION range; the top of the range is the STANDARD. Phase 2 = the 0 exercises + the grade 2 exercises. ◇ PICK 1 = choose one. Every cell is a per-set prescription.</t>
         </is>
       </c>
     </row>
@@ -1197,7 +863,7 @@
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>PHASE 3 · VERTICAL STRAIGHT ARM PULL · 2 sets</t>
+          <t>PHASE 2 · VERTICAL STRAIGHT ARM PULL · 2 sets</t>
         </is>
       </c>
     </row>
@@ -1211,39 +877,39 @@
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>○  3</t>
+          <t>○  2</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Inverted hang tuck to pencil leg lift</t>
+          <t>Active Hang Hold</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>12 reps, full inverted hang each rep</t>
+          <t>45s hold, scapula depression</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>6–12 reps</t>
+          <t>20–45s</t>
         </is>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>○  3</t>
+          <t>○  2</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Single arm assisted scapula pull-up</t>
+          <t>Scapula Pull-ups</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>12 scapula pull downs each arm</t>
+          <t>15 reps, 1s hold at top</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
@@ -1255,44 +921,44 @@
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>○  3</t>
+          <t>○  2</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Alternating Tuck L sit</t>
+          <t>Feet Assisted Arching Active Hang</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>45s hold (active hang)</t>
+          <t>15 reps, arms straight</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>20–45s</t>
+          <t>5–15 reps</t>
         </is>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>○  3</t>
+          <t>○  0</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Active Tuck to L Sit Eccentrics</t>
+          <t>1 Arm Cable Scapular Pulldown</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>10 reps, feet parallel to hips</t>
+          <t>10 reps at 40% bodyweight</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>6–10 reps</t>
+          <t>8–10 reps @ 20–30% BW</t>
         </is>
       </c>
     </row>
@@ -1304,17 +970,17 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>1 Arm Cable Scapular Pulldown</t>
+          <t>Overhead banded Pullaparts</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>10 reps at 40% bodyweight</t>
+          <t>20 reps with a medium resistance band</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>8–10 reps @ 30–40% BW</t>
+          <t>20 reps · light–medium resistance band</t>
         </is>
       </c>
     </row>
@@ -1326,17 +992,17 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Overhead banded Pullaparts</t>
+          <t>Banded Pull Aparts</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>20 reps with a medium resistance band</t>
+          <t>15 reps medium resistance band</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>20 reps · light–medium resistance band</t>
+          <t>15 reps · light–medium resistance band</t>
         </is>
       </c>
     </row>
@@ -1348,17 +1014,17 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Banded Pull Aparts</t>
+          <t>Banded Pulldowns</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>15 reps medium resistance band</t>
+          <t>20 reps with medium intensity band</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>15 reps · light–medium resistance band</t>
+          <t>20 reps · light–medium resistance band</t>
         </is>
       </c>
     </row>
@@ -1370,17 +1036,17 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Banded Pulldowns</t>
+          <t>Lateral Cable Pulldowns</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>20 reps with medium intensity band</t>
+          <t>12 reps with 15% bodyweight</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>20 reps · light–medium resistance band</t>
+          <t>12 reps @ 5–15% BW</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1058,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Lateral Cable Pulldowns</t>
+          <t>DB Lat Pullover</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -1406,30 +1072,8 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>○  0</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>DB Lat Pullover</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>12 reps with 15% bodyweight</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>12 reps @ 5–15% BW</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="14">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="D11:F11"/>
     <mergeCell ref="D13:F13"/>
@@ -1440,6 +1084,368 @@
     <mergeCell ref="D12:F12"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="D9:F9"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="D10:F10"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId9"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="8.710000000000001" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="31.5" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TRAIN A SKILL — LEVEL 1  ·  HANGING L SIT  ·  PHASE 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Self-paced — stay on each exercise until the standard is earned. Train inside the PRESCRIPTION range; the top of the range is the STANDARD. Phase 3 = the 0 exercises + the grade 3 exercises. ◇ PICK 1 = choose one. Every cell is a per-set prescription.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="21.75" customHeight="1">
+      <c r="A4" s="3" t="n"/>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>EXERCISE</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>PRESCRIPTION</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18.75" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>PHASE 3 · VERTICAL STRAIGHT ARM PULL · 2 sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>◇  PICK 1  —  interchangeable, choose one</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>○  3</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Active Tuck Hang Reps</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>15 reps, knees in line with hips</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>5–15 reps</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>○  3</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Active Tuck Hang Hold</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>45s hold, knees in line with hips</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>20–45s</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>○  3</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Inverted hang tuck to pencil leg lift</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>12 reps, full inverted hang each rep</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>6–12 reps</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>○  4</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Single arm assisted scapula pull-up</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>12 scapula pull downs each arm</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>5–15 reps</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>○  4</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Alternating Tuck L sit</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>45s hold (active hang)</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>20–45s</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>○  4</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Active Tuck to L Sit Eccentrics</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>10 reps, feet parallel to hips</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>6–10 reps</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>1 Arm Cable Scapular Pulldown</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>10 reps at 40% bodyweight</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>8–10 reps @ 30–40% BW</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Overhead banded Pullaparts</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>20 reps with a medium resistance band</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>20 reps · light–medium resistance band</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Banded Pull Aparts</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>15 reps medium resistance band</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>15 reps · light–medium resistance band</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Banded Pulldowns</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>20 reps with medium intensity band</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>20 reps · light–medium resistance band</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Lateral Cable Pulldowns</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>12 reps with 15% bodyweight</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>12 reps @ 5–15% BW</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>DB Lat Pullover</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>12 reps with 15% bodyweight</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>12 reps @ 5–15% BW</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="17">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="D17:F17"/>
     <mergeCell ref="D7:F7"/>
     <mergeCell ref="D8:F8"/>
     <mergeCell ref="D15:F15"/>
@@ -1457,6 +1463,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -1520,22 +1528,22 @@
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>✦</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>TEST: Hanging L Sit</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>PASS: 30 second hold</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>10–30s · 2 sets  ✦</t>
         </is>
